--- a/docs/migration-orders/prompt-to-claude-code/antigravity/migration-process-handbook-antigravity-v5.xlsx
+++ b/docs/migration-orders/prompt-to-claude-code/antigravity/migration-process-handbook-antigravity-v5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SaaS Project\trading-alerts-saas-public\docs\migration-orders\prompt-to-claude-code\antigravity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6396F5-2B33-4A98-9378-BA76EDC0AB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336A5341-40B0-483A-BE45-1DF0166D7CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3484,7 +3484,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3561,6 +3561,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -3589,7 +3595,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3746,6 +3752,9 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10448,7 +10457,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="69" customFormat="1" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:18" s="35" customFormat="1" ht="158.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="31">
         <v>58</v>
       </c>
@@ -10467,40 +10476,40 @@
       <c r="F59" s="34" t="s">
         <v>854</v>
       </c>
-      <c r="G59" s="68" t="s">
+      <c r="G59" s="34" t="s">
         <v>1058</v>
       </c>
-      <c r="H59" s="68" t="s">
+      <c r="H59" s="34" t="s">
         <v>599</v>
       </c>
-      <c r="I59" s="68" t="s">
-        <v>591</v>
-      </c>
-      <c r="J59" s="68" t="s">
+      <c r="I59" s="34" t="s">
+        <v>591</v>
+      </c>
+      <c r="J59" s="34" t="s">
         <v>600</v>
       </c>
-      <c r="K59" s="68" t="s">
+      <c r="K59" s="34" t="s">
         <v>855</v>
       </c>
-      <c r="L59" s="68" t="s">
+      <c r="L59" s="34" t="s">
         <v>856</v>
       </c>
-      <c r="M59" s="68" t="s">
+      <c r="M59" s="34" t="s">
         <v>857</v>
       </c>
-      <c r="N59" s="68" t="s">
+      <c r="N59" s="34" t="s">
         <v>595</v>
       </c>
-      <c r="O59" s="68" t="s">
-        <v>591</v>
-      </c>
-      <c r="P59" s="68" t="s">
-        <v>591</v>
-      </c>
-      <c r="Q59" s="68" t="s">
+      <c r="O59" s="34" t="s">
+        <v>591</v>
+      </c>
+      <c r="P59" s="34" t="s">
+        <v>591</v>
+      </c>
+      <c r="Q59" s="34" t="s">
         <v>858</v>
       </c>
-      <c r="R59" s="68" t="s">
+      <c r="R59" s="34" t="s">
         <v>591</v>
       </c>
     </row>
@@ -10604,7 +10613,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="35" customFormat="1" ht="172.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:18" s="69" customFormat="1" ht="172.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="31">
         <v>61</v>
       </c>
@@ -10621,36 +10630,36 @@
       <c r="F62" s="34" t="s">
         <v>867</v>
       </c>
-      <c r="G62" s="34" t="s">
+      <c r="G62" s="71" t="s">
         <v>868</v>
       </c>
-      <c r="H62" s="34" t="s">
+      <c r="H62" s="68" t="s">
         <v>599</v>
       </c>
-      <c r="I62" s="34" t="s">
-        <v>591</v>
-      </c>
-      <c r="J62" s="34" t="s">
+      <c r="I62" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="J62" s="71" t="s">
         <v>600</v>
       </c>
-      <c r="K62" s="34" t="s">
+      <c r="K62" s="71" t="s">
         <v>869</v>
       </c>
-      <c r="L62" s="33"/>
-      <c r="M62" s="33"/>
-      <c r="N62" s="34" t="s">
+      <c r="L62" s="42"/>
+      <c r="M62" s="42"/>
+      <c r="N62" s="68" t="s">
         <v>595</v>
       </c>
-      <c r="O62" s="34" t="s">
-        <v>591</v>
-      </c>
-      <c r="P62" s="34" t="s">
-        <v>591</v>
-      </c>
-      <c r="Q62" s="34" t="s">
+      <c r="O62" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="P62" s="68" t="s">
+        <v>591</v>
+      </c>
+      <c r="Q62" s="71" t="s">
         <v>870</v>
       </c>
-      <c r="R62" s="34" t="s">
+      <c r="R62" s="68" t="s">
         <v>591</v>
       </c>
     </row>
